--- a/_data/Prednasky_2017.xlsx
+++ b/_data/Prednasky_2017.xlsx
@@ -5,14 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="Prednasky_2017_2" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Prednasky_2021" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Prednasky_2022" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Prednasky_2023" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Prednasky_2024" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Prednasky_2017_2" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Prednasky_2021" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Prednasky_2022" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Prednasky_2023" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Prednasky_2024" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Prednasky_2025" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="860">
   <si>
     <t xml:space="preserve">Prednasejici</t>
   </si>
@@ -3534,6 +3535,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">🎤</t>
     </r>
@@ -3547,6 +3549,267 @@
       </rPr>
       <t xml:space="preserve">Výuka informatiky na neinformatické fakultě</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Důvěra a pocit zodpovědnosti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1Vf_VPYg9ZwbctQzN98IyG47aBDnp1Y95edhA5gDfR1o/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 JS v kleci aneb jak zkrotit doplňky třetích stran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1CFEKhfSr9UwSiln2vor-sSJR-r0ILTFl09DstVjpgJY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Hampl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Vektorové DB v PostgreSQL snadno a rychle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1pAxAfbSOnxUbEZR76edS7LCoebjRgsdjxiSAZSh7GWY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Walking desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1d1qXwD4w-y1Y5FlbzXmqc1rdo8ZjIs9NDck_z39sHDI/edit?slide=id.p#slide=id.p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 CI/CD Capture &amp; Iterate / Compose &amp; Develop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1baofQPtOptpMkWzE3mQs7pgcmA3QcGPwpBu81ySnVuc/edit?usp=drivesdk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vlaďka Janů</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Budoucnost energetiky a je vodík naše budoucnost?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1ZVa8tlptD4ETx3_L0R41AwlpGqD-ZeYbGGPoIsNKR-s/edit?slide=id.p#slide=id.p </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Nemám téma - to bude pořádná ledová sprcha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 IDDQD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 InfluxDB a proč ho (ne)používat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1nQlBARhHV9sraosAbuwx4jwzlqiQuRVMPJQrrmI-UrY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Hacker's TTL - Hacker's Time To Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1DX90VUUTQTHT4s85VBWBN43GBFirI8lzUOLZtO3TJvE/edit?slide=id.p#slide=id.p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Závislosti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/14LRfxMPL2mMEI-m1Xrv7GKwOtkhsB_-kQ41UEjqoyt4/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Když pravá ruka neví, co dělá ta levá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.actiwerks.com/presentations/HomomorphicEncryption.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Event Sourcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1iskzWRg4N3dLp9iWLrXWqt7_GeYrRWu9w4msvO9Sd0A/edit?slide=id.p#slide=id.p </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Switch to Event Sourcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1vrWq4I1eDehxUYT2vJzd90yOBvb0GH6lFhxnh7ZybgY/edit?slide=id.p#slide=id.p </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Jízda na spotřebu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://bit.ly/4nzz7Sg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 ESPHome - DIY gadgety pro domácí automatizaci snadno a rychle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1_gIeV3Yayd_yd0I7VBb5o6fDBwgqjD10fyieUisVUrg/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Váš první shader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1_k_a5E8ChJOP4pi_QMeZALAaT7QCg3k6Hqj6-Gswnlw/edit?slide=id.g38464b7e565_0_0#slide=id.g38464b7e565_0_0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Jak se plánuje doprava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1Lnc1VZmC_yCS0myQd7eYpR3um5HdpwRAUPBwSV7u4_Y/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Renesance pirátění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1G3819kDuzcq-0tqje3yindOIFtZd3alqyOA_k_wKDOw/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Hiring is Hard!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiring is Hard! - jOpenSpace 2025.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 The future is vibe-coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1cX-y_wwQJBrKBl4Fk9SuXiXLDtkgMdtQwX0sea0oIe4/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Přibližné výpočty v dobách AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://minily.org/jopenspace2025-ivoshm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filip Sedllák</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Rekonstrukce domu z první republiky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1Tz-NWpJbeVC8LHxkpTAc0NHV8kY0rx9Ny9vroMVVdHc/edit?slide=id.g38906502ce2_0_63#slide=id.g38906502ce2_0_63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Orchestrace AI agentu s autogen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1ufyRBMFrCzOMf2s-DWDc7kbopfJnfdOKIJ0BJGNHia4/edit?slide=id.p1#slide=id.p1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martin Dulák</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Sometimes you should over-engineer it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://drive.google.com/file/d/1hFg11Sd2R6f9aYeXqYdbHJGAUOKTtqrG/view?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Frontend-Backend integrace bez bolesti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1HQwwEbBNJQIcf6OTAs8pJy_D20Y0nqOVc06X70Mgfqo/edit?slide=id.g368b57d9771_0_5#slide=id.g368b57d9771_0_5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Git Gud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1J5fJSWM7zRzUkobLcMHHhKTRADeeII_Wvi6oxsBuDfw/edit?slide=id.p#slide=id.p </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomáš Karela Procházka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 gRPC - Looking for magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1_HJsLPXQKMbV31pkUVZu21e63G57YJQwbfe-ei19kKs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Simple guide to remote debugging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://prezi.com/view/CAf5JqoNbJs3T4lpA1pX/?referral_token=S5on9plnB3FN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Technologické bestie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ondra Nekola </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Smrtonosná trojka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vít Kalisz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Jak dostat AI do škol?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1i5-jm2SmBDBC0HV2_fLVSEPoUXw41zy98SM9nWcQ0eA/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lojza Holub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Úvod do Evžena Oněgina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1SoVMWUZTTAbccWIN6PZzVrZ22a-bT59jkDu6jy_C_Ag/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Kubernetes secrets the right way</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1oykfG53Luetf6qS9rQbfVchJPLp5Z5aspVP3-MJP8SI/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filip Procházka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Devin.AI - basic intro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1OIN85XF82k9_kRgkE9q-imG4W0Vh6CrW2nb0o1muUD0/edit </t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Knížka v lahvi pro 21. století</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1FNRG9AFQwtfVy7D1UixxgZ4EYxmRnamw2_TD8189Mo0/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 oscloud.cz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1hIApwqazJV29sxGV9bQLlB3Dih1ITAlFZtau88jM0CY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Nesportujte s dětmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/183ChRmG69cV7aB0YapOgMYxji5wGK0fM_lPcdvOMEBE/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 JavaEE =&gt; JakartaEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1s2GhXAiMA9MEqqI9qdawnF3HMOACa7s9wYvEQ9A3-Mk/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">🎤 Debugging Infrastructure Performance Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1-pgcRAKRvaAMc9bQP3-BBffMF3YQQ5viYzAzoDalAWY/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Better outputs of AI coding tools via feedback loops from stricter code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://docs.google.com/presentation/d/1BCavpivXPhLGHtPYNg60fjXb8o-m84FmXzsfMUQr0nI/edit </t>
   </si>
 </sst>
 </file>
@@ -3613,6 +3876,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3681,20 +3945,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3702,7 +3966,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3714,15 +3978,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3799,832 +4067,938 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F43"/>
-  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="57.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="49.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="130.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="0" t="s">
+      <c r="E18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E20" s="0" t="s">
+      <c r="E20" s="1" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E21" s="0" t="s">
+      <c r="E21" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E22" s="0" t="s">
+      <c r="E22" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="0" t="s">
+      <c r="E23" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E24" s="0" t="s">
+      <c r="E24" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D25" s="0" t="s">
+      <c r="D25" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="0" t="s">
+      <c r="E25" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E27" s="0" t="s">
+      <c r="E27" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D28" s="0" t="s">
+      <c r="D28" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E28" s="0" t="s">
+      <c r="E28" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="0" t="s">
+      <c r="E29" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="0" t="s">
+      <c r="E30" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="0" t="s">
+      <c r="D31" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E31" s="0" t="s">
+      <c r="E31" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="0" t="s">
+      <c r="E32" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="0" t="s">
+      <c r="D33" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E33" s="0" t="s">
+      <c r="E33" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D34" s="0" t="s">
+      <c r="D34" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E34" s="0" t="s">
+      <c r="E34" s="1" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D35" s="0" t="s">
+      <c r="D35" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="D36" s="0" t="s">
+      <c r="D36" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E36" s="0" t="s">
+      <c r="E36" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D37" s="0" t="s">
+      <c r="D37" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="E37" s="0" t="s">
+      <c r="E37" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C38" s="0" t="s">
+      <c r="C38" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D38" s="0" t="s">
+      <c r="D38" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="D39" s="0" t="s">
+      <c r="D39" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="E39" s="0" t="s">
+      <c r="E39" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D40" s="0" t="s">
+      <c r="D40" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="E40" s="0" t="s">
+      <c r="E40" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="E41" s="1" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+      <c r="A42" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="D42" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
+      <c r="A43" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C43" s="0" t="s">
+      <c r="C43" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D43" s="0" t="s">
+      <c r="D43" s="1" t="s">
         <v>238</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -4633,50 +5007,50 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="14.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="57.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="49.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="30.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="33.82"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="3" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="8.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="1448.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>240</v>
       </c>
       <c r="E2" s="4"/>
@@ -4684,169 +5058,169 @@
         <v>241</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="986.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="494" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+    <row r="5" customFormat="false" ht="882.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="822.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>254</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="494" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>259</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="419.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="867.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>267</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="494" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>271</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="926.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>276</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+    <row r="12" customFormat="false" ht="583.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="13" customFormat="false" ht="702.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>284</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -4856,212 +5230,212 @@
         <v>286</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+    <row r="14" customFormat="false" ht="732.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>288</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+    <row r="15" customFormat="false" ht="807.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+    <row r="16" customFormat="false" ht="822.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>295</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+    <row r="17" customFormat="false" ht="971.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>299</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+    <row r="18" customFormat="false" ht="568.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>303</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+    <row r="19" customFormat="false" ht="1016.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>307</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+    <row r="20" customFormat="false" ht="792.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>312</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="21" customFormat="false" ht="598.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+    <row r="22" customFormat="false" ht="688.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>321</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+    <row r="23" customFormat="false" ht="658.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="24" customFormat="false" ht="359.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+    <row r="25" customFormat="false" ht="508.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>333</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="1"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="1"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="1"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="1"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="1"/>
+      <c r="D41" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5084,8 +5458,8 @@
     <hyperlink ref="E25" r:id="rId17" display="https://www.dynatrace.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5094,39 +5468,39 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="14.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="57.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="49.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="30.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="128.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="33.82"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="3" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="57.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="49.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="128.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="8.72"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5137,10 +5511,10 @@
       <c r="B2" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>338</v>
       </c>
       <c r="E2" s="6" t="s">
@@ -5157,13 +5531,13 @@
       <c r="B3" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>342</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>344</v>
       </c>
     </row>
@@ -5177,13 +5551,13 @@
       <c r="C4" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>348</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>349</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5197,13 +5571,13 @@
       <c r="C5" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>353</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>355</v>
       </c>
     </row>
@@ -5217,13 +5591,13 @@
       <c r="C6" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>358</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>360</v>
       </c>
     </row>
@@ -5234,16 +5608,16 @@
       <c r="B7" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>363</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>365</v>
       </c>
     </row>
@@ -5254,10 +5628,10 @@
       <c r="B8" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>369</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -5274,16 +5648,16 @@
       <c r="B9" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>374</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>376</v>
       </c>
     </row>
@@ -5297,13 +5671,13 @@
       <c r="C10" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>379</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>381</v>
       </c>
     </row>
@@ -5314,16 +5688,16 @@
       <c r="B11" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>384</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>386</v>
       </c>
     </row>
@@ -5337,13 +5711,13 @@
       <c r="C12" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>389</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>390</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>391</v>
       </c>
     </row>
@@ -5357,7 +5731,7 @@
       <c r="C13" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="2" t="s">
         <v>395</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -5377,13 +5751,13 @@
       <c r="C14" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>401</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>402</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>403</v>
       </c>
     </row>
@@ -5394,16 +5768,16 @@
       <c r="B15" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="2" t="s">
         <v>407</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>409</v>
       </c>
     </row>
@@ -5414,16 +5788,16 @@
       <c r="B16" s="5" t="s">
         <v>410</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>412</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>414</v>
       </c>
     </row>
@@ -5437,13 +5811,13 @@
       <c r="C17" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="2" t="s">
         <v>418</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>419</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>420</v>
       </c>
     </row>
@@ -5454,16 +5828,16 @@
       <c r="B18" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="2" t="s">
         <v>424</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>426</v>
       </c>
     </row>
@@ -5474,16 +5848,16 @@
       <c r="B19" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="2" t="s">
         <v>429</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>431</v>
       </c>
     </row>
@@ -5497,13 +5871,13 @@
       <c r="C20" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="2" t="s">
         <v>435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>437</v>
       </c>
     </row>
@@ -5514,16 +5888,16 @@
       <c r="B21" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C21" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="2" t="s">
         <v>441</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>442</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>443</v>
       </c>
     </row>
@@ -5534,16 +5908,16 @@
       <c r="B22" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C22" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="2" t="s">
         <v>446</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>448</v>
       </c>
     </row>
@@ -5554,16 +5928,16 @@
       <c r="B23" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="2" t="s">
         <v>451</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>452</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="1" t="s">
         <v>453</v>
       </c>
     </row>
@@ -5577,13 +5951,13 @@
       <c r="C24" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>456</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>458</v>
       </c>
     </row>
@@ -5594,33 +5968,33 @@
       <c r="B25" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="2" t="s">
         <v>462</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>464</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D26" s="1"/>
+      <c r="D26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D27" s="1"/>
+      <c r="D27" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D29" s="1"/>
+      <c r="D29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D30" s="1"/>
+      <c r="D30" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D41" s="1"/>
+      <c r="D41" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5660,8 +6034,8 @@
     <hyperlink ref="E25" r:id="rId34" display="https://docs.google.com/presentation/d/1olGUm4FSi8sIMxrWY9B4VKZ-9hDB_Ow0GLdGZLuH12Y/edit?usp=sharing"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -5670,56 +6044,56 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="14.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.72265625" defaultRowHeight="14.5" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="17.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="68.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="43.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="30.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="69.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="33.82"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="3" width="8.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="68.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="43.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="69.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="33.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="7" style="1" width="8.72"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="14.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>468</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -5727,119 +6101,119 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>478</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>483</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>488</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="1" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>499</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -5847,96 +6221,96 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>510</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>511</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="1" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="1" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>521</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="1" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>526</v>
       </c>
       <c r="E13" s="7" t="s">
@@ -5947,572 +6321,571 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="1" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="1" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="1" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>544</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>545</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>546</v>
       </c>
       <c r="E17" s="6"/>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="1" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="1" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="1" t="s">
         <v>558</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>560</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>562</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="1" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>569</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="1" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="1" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="3" t="s">
+      <c r="E23" s="3"/>
+      <c r="F23" s="1" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>584</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>585</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="1" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="C25" s="1" t="s">
         <v>589</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>590</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="1" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>594</v>
       </c>
-      <c r="C26" s="0" t="s">
+      <c r="C26" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="1" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C27" s="0" t="s">
+      <c r="C27" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="1" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="C28" s="0" t="s">
+      <c r="C28" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="3" t="s">
+      <c r="E28" s="3"/>
+      <c r="F28" s="1" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>608</v>
       </c>
-      <c r="C29" s="0" t="s">
+      <c r="C29" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="1" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>612</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="1" t="s">
         <v>615</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="C31" s="0" t="s">
+      <c r="C31" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="F31" s="3" t="s">
+      <c r="F31" s="1" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="1" t="s">
         <v>627</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="F33" s="3" t="s">
+      <c r="F33" s="1" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="18.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="C34" s="0" t="s">
+      <c r="C34" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="F34" s="1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="C35" s="0" t="s">
+      <c r="C35" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="F35" s="3" t="s">
+      <c r="F35" s="1" t="s">
         <v>643</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="C36" s="0" t="s">
+      <c r="C36" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="F36" s="3" t="s">
+      <c r="F36" s="1" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C37" s="0" t="s">
+      <c r="C37" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F37" s="1" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="C38" s="0"/>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F38" s="1" t="s">
         <v>658</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="C39" s="0" t="s">
+      <c r="C39" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F39" s="1" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="C40" s="0" t="s">
+      <c r="C40" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="F40" s="3" t="s">
+      <c r="F40" s="1" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="C41" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F41" s="1" t="s">
         <v>674</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="C42" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="F42" s="3" t="s">
+      <c r="F42" s="1" t="s">
         <v>679</v>
       </c>
     </row>
@@ -6555,8 +6928,8 @@
     <hyperlink ref="E42" r:id="rId35" display="https://drive.google.com/file/d/1k4MXGV0XhDE0v8fae_wMNGVKgxWQpbek/view?usp=sharing"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -6565,474 +6938,474 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="51.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="51.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="35.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="108.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="23.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="51.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="35.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="108.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="56.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>682</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>684</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>690</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>692</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>700</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="E12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="2" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="2" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>723</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="2" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="2" t="s">
         <v>731</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="2" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="2" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="2" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>740</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="2" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="2" t="s">
         <v>746</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="2" t="s">
         <v>751</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>752</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="2" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="2" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="2" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>581</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="C33" s="0" t="s">
+      <c r="C33" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="2" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="2" t="s">
         <v>766</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="2" t="s">
         <v>767</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>769</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="2" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
         <v>771</v>
       </c>
       <c r="B36" s="10" t="s">
@@ -7092,7 +7465,555 @@
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="0" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="false" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="141.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="56.34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>773</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>775</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>777</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>778</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>780</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="E5" s="11" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>782</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="E6" s="11" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>784</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>785</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="E7" s="11" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>787</v>
+      </c>
+      <c r="E8" s="11"/>
+    </row>
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>788</v>
+      </c>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="E10" s="11" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>791</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="E11" s="11" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>793</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>795</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="E14" s="11" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>799</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>801</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="11" t="s">
+        <v>743</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>803</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>805</v>
+      </c>
+      <c r="C18" s="2"/>
+      <c r="E18" s="11" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>807</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="E19" s="11" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>809</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="E20" s="11" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="11" t="s">
+        <v>593</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>811</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>739</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>813</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="E22" s="11" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>815</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="E23" s="11" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>817</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>818</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="E24" s="11" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>820</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>822</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>823</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="E26" s="11" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>825</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="E27" s="11" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>827</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="11" t="s">
+        <v>829</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>830</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>832</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>834</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
+        <v>835</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>836</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="E32" s="11"/>
+    </row>
+    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
+        <v>837</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>838</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="11" t="s">
+        <v>840</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="E34" s="11" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>843</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="s">
+        <v>845</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>856</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>858</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>859</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="https://docs.google.com/presentation/d/1Vf_VPYg9ZwbctQzN98IyG47aBDnp1Y95edhA5gDfR1o/edit?usp=sharing"/>
+    <hyperlink ref="E3" r:id="rId2" display="https://docs.google.com/presentation/d/1CFEKhfSr9UwSiln2vor-sSJR-r0ILTFl09DstVjpgJY/edit?usp=sharing"/>
+    <hyperlink ref="E4" r:id="rId3" display="https://docs.google.com/presentation/d/1pAxAfbSOnxUbEZR76edS7LCoebjRgsdjxiSAZSh7GWY/edit?usp=sharing"/>
+    <hyperlink ref="E5" r:id="rId4" location="slide=id.p" display="https://docs.google.com/presentation/d/1d1qXwD4w-y1Y5FlbzXmqc1rdo8ZjIs9NDck_z39sHDI/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="E6" r:id="rId5" display="https://docs.google.com/presentation/d/1baofQPtOptpMkWzE3mQs7pgcmA3QcGPwpBu81ySnVuc/edit?usp=drivesdk"/>
+    <hyperlink ref="E7" r:id="rId6" location="slide=id.p" display="https://docs.google.com/presentation/d/1ZVa8tlptD4ETx3_L0R41AwlpGqD-ZeYbGGPoIsNKR-s/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="E10" r:id="rId7" display="https://docs.google.com/presentation/d/1nQlBARhHV9sraosAbuwx4jwzlqiQuRVMPJQrrmI-UrY/edit?usp=sharing"/>
+    <hyperlink ref="E11" r:id="rId8" location="slide=id.p" display="https://docs.google.com/presentation/d/1DX90VUUTQTHT4s85VBWBN43GBFirI8lzUOLZtO3TJvE/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="E12" r:id="rId9" display="https://docs.google.com/presentation/d/14LRfxMPL2mMEI-m1Xrv7GKwOtkhsB_-kQ41UEjqoyt4/edit?usp=sharing"/>
+    <hyperlink ref="E13" r:id="rId10" display="https://www.actiwerks.com/presentations/HomomorphicEncryption.pdf"/>
+    <hyperlink ref="E14" r:id="rId11" location="slide=id.p" display="https://docs.google.com/presentation/d/1iskzWRg4N3dLp9iWLrXWqt7_GeYrRWu9w4msvO9Sd0A/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="E15" r:id="rId12" location="slide=id.p" display="https://docs.google.com/presentation/d/1vrWq4I1eDehxUYT2vJzd90yOBvb0GH6lFhxnh7ZybgY/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="E16" r:id="rId13" display="https://bit.ly/4nzz7Sg"/>
+    <hyperlink ref="E17" r:id="rId14" display="https://docs.google.com/presentation/d/1_gIeV3Yayd_yd0I7VBb5o6fDBwgqjD10fyieUisVUrg/edit?usp=sharing"/>
+    <hyperlink ref="E18" r:id="rId15" location="slide=id.g38464b7e565_0_0" display="https://docs.google.com/presentation/d/1_k_a5E8ChJOP4pi_QMeZALAaT7QCg3k6Hqj6-Gswnlw/edit?slide=id.g38464b7e565_0_0#slide=id.g38464b7e565_0_0"/>
+    <hyperlink ref="E19" r:id="rId16" display="https://docs.google.com/presentation/d/1Lnc1VZmC_yCS0myQd7eYpR3um5HdpwRAUPBwSV7u4_Y/edit?usp=sharing"/>
+    <hyperlink ref="E20" r:id="rId17" display="https://docs.google.com/presentation/d/1G3819kDuzcq-0tqje3yindOIFtZd3alqyOA_k_wKDOw/edit?usp=sharing"/>
+    <hyperlink ref="E21" r:id="rId18" display="Hiring is Hard! - jOpenSpace 2025.pdf"/>
+    <hyperlink ref="E22" r:id="rId19" display="https://docs.google.com/presentation/d/1cX-y_wwQJBrKBl4Fk9SuXiXLDtkgMdtQwX0sea0oIe4/edit?usp=sharing"/>
+    <hyperlink ref="E23" r:id="rId20" display="https://minily.org/jopenspace2025-ivoshm"/>
+    <hyperlink ref="E24" r:id="rId21" location="slide=id.g38906502ce2_0_63" display="https://docs.google.com/presentation/d/1Tz-NWpJbeVC8LHxkpTAc0NHV8kY0rx9Ny9vroMVVdHc/edit?slide=id.g38906502ce2_0_63#slide=id.g38906502ce2_0_63"/>
+    <hyperlink ref="E25" r:id="rId22" location="slide=id.p1" display="https://docs.google.com/presentation/d/1ufyRBMFrCzOMf2s-DWDc7kbopfJnfdOKIJ0BJGNHia4/edit?slide=id.p1#slide=id.p1"/>
+    <hyperlink ref="E26" r:id="rId23" display="https://drive.google.com/file/d/1hFg11Sd2R6f9aYeXqYdbHJGAUOKTtqrG/view?usp=sharing"/>
+    <hyperlink ref="E27" r:id="rId24" location="slide=id.g368b57d9771_0_5" display="https://docs.google.com/presentation/d/1HQwwEbBNJQIcf6OTAs8pJy_D20Y0nqOVc06X70Mgfqo/edit?slide=id.g368b57d9771_0_5#slide=id.g368b57d9771_0_5"/>
+    <hyperlink ref="E28" r:id="rId25" location="slide=id.p" display="https://docs.google.com/presentation/d/1J5fJSWM7zRzUkobLcMHHhKTRADeeII_Wvi6oxsBuDfw/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="E29" r:id="rId26" display="https://docs.google.com/presentation/d/1_HJsLPXQKMbV31pkUVZu21e63G57YJQwbfe-ei19kKs"/>
+    <hyperlink ref="E30" r:id="rId27" display="https://prezi.com/view/CAf5JqoNbJs3T4lpA1pX/?referral_token=S5on9plnB3FN"/>
+    <hyperlink ref="E33" r:id="rId28" display="https://docs.google.com/presentation/d/1i5-jm2SmBDBC0HV2_fLVSEPoUXw41zy98SM9nWcQ0eA/edit?usp=sharing"/>
+    <hyperlink ref="E34" r:id="rId29" display="https://docs.google.com/presentation/d/1SoVMWUZTTAbccWIN6PZzVrZ22a-bT59jkDu6jy_C_Ag/edit?usp=sharing"/>
+    <hyperlink ref="E35" r:id="rId30" display="https://docs.google.com/presentation/d/1oykfG53Luetf6qS9rQbfVchJPLp5Z5aspVP3-MJP8SI/edit?usp=sharing"/>
+    <hyperlink ref="E36" r:id="rId31" display="https://docs.google.com/presentation/d/1OIN85XF82k9_kRgkE9q-imG4W0Vh6CrW2nb0o1muUD0/edit"/>
+    <hyperlink ref="E37" r:id="rId32" display="https://docs.google.com/presentation/d/1FNRG9AFQwtfVy7D1UixxgZ4EYxmRnamw2_TD8189Mo0/edit?usp=sharing"/>
+    <hyperlink ref="B38" r:id="rId33" display="🎤 oscloud.cz"/>
+    <hyperlink ref="E38" r:id="rId34" display="https://docs.google.com/presentation/d/1hIApwqazJV29sxGV9bQLlB3Dih1ITAlFZtau88jM0CY/edit?usp=sharing"/>
+    <hyperlink ref="E39" r:id="rId35" display="https://docs.google.com/presentation/d/183ChRmG69cV7aB0YapOgMYxji5wGK0fM_lPcdvOMEBE/edit?usp=sharing"/>
+    <hyperlink ref="E40" r:id="rId36" display="https://docs.google.com/presentation/d/1s2GhXAiMA9MEqqI9qdawnF3HMOACa7s9wYvEQ9A3-Mk/edit?usp=sharing"/>
+    <hyperlink ref="E41" r:id="rId37" display="https://docs.google.com/presentation/d/1-pgcRAKRvaAMc9bQP3-BBffMF3YQQ5viYzAzoDalAWY/edit?usp=sharing"/>
+    <hyperlink ref="E42" r:id="rId38" display="https://docs.google.com/presentation/d/1BCavpivXPhLGHtPYNg60fjXb8o-m84FmXzsfMUQr0nI/edit"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/_data/Prednasky_2017.xlsx
+++ b/_data/Prednasky_2017.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1005" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="870">
   <si>
     <t xml:space="preserve">Prednasejici</t>
   </si>
@@ -3599,6 +3599,9 @@
     <t xml:space="preserve">🎤 IDDQD</t>
   </si>
   <si>
+    <t xml:space="preserve">https://blog.zvestov.cz</t>
+  </si>
+  <si>
     <t xml:space="preserve">🎤 InfluxDB a proč ho (ne)používat</t>
   </si>
   <si>
@@ -3620,6 +3623,9 @@
     <t xml:space="preserve">🎤 Když pravá ruka neví, co dělá ta levá</t>
   </si>
   <si>
+    <t xml:space="preserve">www.actiwerks.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.actiwerks.com/presentations/HomomorphicEncryption.pdf</t>
   </si>
   <si>
@@ -3692,6 +3698,9 @@
     <t xml:space="preserve">https://docs.google.com/presentation/d/1Tz-NWpJbeVC8LHxkpTAc0NHV8kY0rx9Ny9vroMVVdHc/edit?slide=id.g38906502ce2_0_63#slide=id.g38906502ce2_0_63</t>
   </si>
   <si>
+    <t xml:space="preserve">Vojtěch Růžicka</t>
+  </si>
+  <si>
     <t xml:space="preserve">🎤 Orchestrace AI agentu s autogen</t>
   </si>
   <si>
@@ -3704,6 +3713,9 @@
     <t xml:space="preserve">🎤 Sometimes you should over-engineer it</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.linkedin.com/in/dulak/</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://drive.google.com/file/d/1hFg11Sd2R6f9aYeXqYdbHJGAUOKTtqrG/view?usp=sharing</t>
   </si>
   <si>
@@ -3743,12 +3755,18 @@
     <t xml:space="preserve">🎤 Smrtonosná trojka</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.nekola.cz</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vít Kalisz</t>
   </si>
   <si>
     <t xml:space="preserve">🎤 Jak dostat AI do škol?</t>
   </si>
   <si>
+    <t xml:space="preserve">notnullmakers.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://docs.google.com/presentation/d/1i5-jm2SmBDBC0HV2_fLVSEPoUXw41zy98SM9nWcQ0eA/edit?usp=sharing</t>
   </si>
   <si>
@@ -3758,6 +3776,9 @@
     <t xml:space="preserve">🎤 Úvod do Evžena Oněgina</t>
   </si>
   <si>
+    <t xml:space="preserve">https://commity.cz</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://docs.google.com/presentation/d/1SoVMWUZTTAbccWIN6PZzVrZ22a-bT59jkDu6jy_C_Ag/edit?usp=sharing</t>
   </si>
   <si>
@@ -3773,12 +3794,18 @@
     <t xml:space="preserve">🎤 Devin.AI - basic intro</t>
   </si>
   <si>
+    <t xml:space="preserve">https://filip-prochazka.com/</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://docs.google.com/presentation/d/1OIN85XF82k9_kRgkE9q-imG4W0Vh6CrW2nb0o1muUD0/edit </t>
   </si>
   <si>
     <t xml:space="preserve">🎤 Knížka v lahvi pro 21. století</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.linkedin.com/in/xxbedy/</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://docs.google.com/presentation/d/1FNRG9AFQwtfVy7D1UixxgZ4EYxmRnamw2_TD8189Mo0/edit?usp=sharing</t>
   </si>
   <si>
@@ -3789,6 +3816,9 @@
   </si>
   <si>
     <t xml:space="preserve">🎤 Nesportujte s dětmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://novoj.net</t>
   </si>
   <si>
     <t xml:space="preserve">https://docs.google.com/presentation/d/183ChRmG69cV7aB0YapOgMYxji5wGK0fM_lPcdvOMEBE/edit?usp=sharing</t>
@@ -7511,463 +7541,517 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="2" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="2" t="s">
         <v>775</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="2" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="2" t="s">
         <v>778</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="2" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="2" t="s">
         <v>780</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="2" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="E6" s="11" t="s">
+      <c r="C6" s="11" t="s">
+        <v>720</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="2" t="s">
         <v>785</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="2" t="s">
         <v>786</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="C9" s="11" t="s">
+        <v>789</v>
+      </c>
+      <c r="E9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>789</v>
+      <c r="B10" s="2" t="s">
+        <v>790</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="E10" s="11" t="s">
-        <v>790</v>
+      <c r="E10" s="2" t="s">
+        <v>791</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>791</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="E11" s="11" t="s">
+      <c r="B11" s="2" t="s">
         <v>792</v>
       </c>
+      <c r="C11" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>793</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>793</v>
-      </c>
-      <c r="E12" s="11" t="s">
+      <c r="B12" s="2" t="s">
         <v>794</v>
       </c>
+      <c r="C12" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>795</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>795</v>
-      </c>
-      <c r="E13" s="11" t="s">
+      <c r="B13" s="2" t="s">
         <v>796</v>
       </c>
+      <c r="C13" s="11" t="s">
+        <v>797</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>797</v>
+      <c r="B14" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="E14" s="11" t="s">
-        <v>798</v>
+      <c r="E14" s="2" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="B15" s="11" t="s">
-        <v>799</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>800</v>
+      <c r="B15" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>801</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>802</v>
+      <c r="B16" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>804</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>803</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="B17" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>745</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>805</v>
-      </c>
-      <c r="C18" s="2"/>
-      <c r="E18" s="11" t="s">
-        <v>806</v>
+      <c r="B18" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>808</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="B19" s="11" t="s">
-        <v>807</v>
-      </c>
-      <c r="C19" s="2"/>
-      <c r="E19" s="11" t="s">
-        <v>808</v>
+      <c r="B19" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>810</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>809</v>
-      </c>
-      <c r="C20" s="2"/>
-      <c r="E20" s="11" t="s">
-        <v>810</v>
+      <c r="B20" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>550</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>811</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>812</v>
+      <c r="B21" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>813</v>
+      <c r="B22" s="2" t="s">
+        <v>815</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="E22" s="11" t="s">
-        <v>814</v>
+      <c r="E22" s="2" t="s">
+        <v>816</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>815</v>
+      <c r="B23" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="E23" s="11" t="s">
-        <v>816</v>
+      <c r="E23" s="2" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="11" t="s">
-        <v>817</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>818</v>
-      </c>
-      <c r="C24" s="2"/>
-      <c r="E24" s="11" t="s">
+      <c r="A24" s="2" t="s">
         <v>819</v>
       </c>
+      <c r="B24" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>821</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>820</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>821</v>
+      <c r="A25" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>824</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
-        <v>822</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>823</v>
-      </c>
-      <c r="C26" s="2"/>
-      <c r="E26" s="11" t="s">
-        <v>824</v>
+      <c r="A26" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>827</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B27" s="11" t="s">
-        <v>825</v>
+      <c r="B27" s="2" t="s">
+        <v>829</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="E27" s="11" t="s">
-        <v>826</v>
+      <c r="E27" s="2" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>827</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>828</v>
+      <c r="B28" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="11" t="s">
-        <v>829</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>830</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>831</v>
+      <c r="A29" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>835</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>832</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>833</v>
+      <c r="B30" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="B31" s="11" t="s">
-        <v>834</v>
+      <c r="B31" s="2" t="s">
+        <v>838</v>
       </c>
       <c r="C31" s="2"/>
       <c r="E31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
-        <v>835</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>836</v>
-      </c>
-      <c r="C32" s="2"/>
-      <c r="E32" s="11"/>
+      <c r="A32" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>841</v>
+      </c>
+      <c r="E32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
-        <v>837</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>838</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>839</v>
+      <c r="A33" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>845</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
-        <v>840</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>841</v>
-      </c>
-      <c r="C34" s="2"/>
-      <c r="E34" s="11" t="s">
-        <v>842</v>
+      <c r="A34" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B35" s="11" t="s">
-        <v>843</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>844</v>
+      <c r="B35" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>851</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
-        <v>845</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>846</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>847</v>
+      <c r="A36" s="2" t="s">
+        <v>852</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>854</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>855</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>848</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>849</v>
+      <c r="B37" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>857</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>858</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="11" t="s">
-        <v>850</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>851</v>
+      <c r="B38" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>860</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B39" s="11" t="s">
-        <v>852</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>853</v>
+      <c r="B39" s="2" t="s">
+        <v>861</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>862</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>863</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>854</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>855</v>
+      <c r="B40" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>865</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>856</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>857</v>
+      <c r="B41" s="2" t="s">
+        <v>866</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>867</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B42" s="11" t="s">
-        <v>858</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>859</v>
+      <c r="B42" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>869</v>
       </c>
     </row>
   </sheetData>
@@ -7976,40 +8060,61 @@
     <hyperlink ref="E3" r:id="rId2" display="https://docs.google.com/presentation/d/1CFEKhfSr9UwSiln2vor-sSJR-r0ILTFl09DstVjpgJY/edit?usp=sharing"/>
     <hyperlink ref="E4" r:id="rId3" display="https://docs.google.com/presentation/d/1pAxAfbSOnxUbEZR76edS7LCoebjRgsdjxiSAZSh7GWY/edit?usp=sharing"/>
     <hyperlink ref="E5" r:id="rId4" location="slide=id.p" display="https://docs.google.com/presentation/d/1d1qXwD4w-y1Y5FlbzXmqc1rdo8ZjIs9NDck_z39sHDI/edit?slide=id.p#slide=id.p"/>
-    <hyperlink ref="E6" r:id="rId5" display="https://docs.google.com/presentation/d/1baofQPtOptpMkWzE3mQs7pgcmA3QcGPwpBu81ySnVuc/edit?usp=drivesdk"/>
-    <hyperlink ref="E7" r:id="rId6" location="slide=id.p" display="https://docs.google.com/presentation/d/1ZVa8tlptD4ETx3_L0R41AwlpGqD-ZeYbGGPoIsNKR-s/edit?slide=id.p#slide=id.p"/>
-    <hyperlink ref="E10" r:id="rId7" display="https://docs.google.com/presentation/d/1nQlBARhHV9sraosAbuwx4jwzlqiQuRVMPJQrrmI-UrY/edit?usp=sharing"/>
-    <hyperlink ref="E11" r:id="rId8" location="slide=id.p" display="https://docs.google.com/presentation/d/1DX90VUUTQTHT4s85VBWBN43GBFirI8lzUOLZtO3TJvE/edit?slide=id.p#slide=id.p"/>
-    <hyperlink ref="E12" r:id="rId9" display="https://docs.google.com/presentation/d/14LRfxMPL2mMEI-m1Xrv7GKwOtkhsB_-kQ41UEjqoyt4/edit?usp=sharing"/>
-    <hyperlink ref="E13" r:id="rId10" display="https://www.actiwerks.com/presentations/HomomorphicEncryption.pdf"/>
-    <hyperlink ref="E14" r:id="rId11" location="slide=id.p" display="https://docs.google.com/presentation/d/1iskzWRg4N3dLp9iWLrXWqt7_GeYrRWu9w4msvO9Sd0A/edit?slide=id.p#slide=id.p"/>
-    <hyperlink ref="E15" r:id="rId12" location="slide=id.p" display="https://docs.google.com/presentation/d/1vrWq4I1eDehxUYT2vJzd90yOBvb0GH6lFhxnh7ZybgY/edit?slide=id.p#slide=id.p"/>
-    <hyperlink ref="E16" r:id="rId13" display="https://bit.ly/4nzz7Sg"/>
-    <hyperlink ref="E17" r:id="rId14" display="https://docs.google.com/presentation/d/1_gIeV3Yayd_yd0I7VBb5o6fDBwgqjD10fyieUisVUrg/edit?usp=sharing"/>
-    <hyperlink ref="E18" r:id="rId15" location="slide=id.g38464b7e565_0_0" display="https://docs.google.com/presentation/d/1_k_a5E8ChJOP4pi_QMeZALAaT7QCg3k6Hqj6-Gswnlw/edit?slide=id.g38464b7e565_0_0#slide=id.g38464b7e565_0_0"/>
-    <hyperlink ref="E19" r:id="rId16" display="https://docs.google.com/presentation/d/1Lnc1VZmC_yCS0myQd7eYpR3um5HdpwRAUPBwSV7u4_Y/edit?usp=sharing"/>
-    <hyperlink ref="E20" r:id="rId17" display="https://docs.google.com/presentation/d/1G3819kDuzcq-0tqje3yindOIFtZd3alqyOA_k_wKDOw/edit?usp=sharing"/>
-    <hyperlink ref="E21" r:id="rId18" display="Hiring is Hard! - jOpenSpace 2025.pdf"/>
-    <hyperlink ref="E22" r:id="rId19" display="https://docs.google.com/presentation/d/1cX-y_wwQJBrKBl4Fk9SuXiXLDtkgMdtQwX0sea0oIe4/edit?usp=sharing"/>
-    <hyperlink ref="E23" r:id="rId20" display="https://minily.org/jopenspace2025-ivoshm"/>
-    <hyperlink ref="E24" r:id="rId21" location="slide=id.g38906502ce2_0_63" display="https://docs.google.com/presentation/d/1Tz-NWpJbeVC8LHxkpTAc0NHV8kY0rx9Ny9vroMVVdHc/edit?slide=id.g38906502ce2_0_63#slide=id.g38906502ce2_0_63"/>
-    <hyperlink ref="E25" r:id="rId22" location="slide=id.p1" display="https://docs.google.com/presentation/d/1ufyRBMFrCzOMf2s-DWDc7kbopfJnfdOKIJ0BJGNHia4/edit?slide=id.p1#slide=id.p1"/>
-    <hyperlink ref="E26" r:id="rId23" display="https://drive.google.com/file/d/1hFg11Sd2R6f9aYeXqYdbHJGAUOKTtqrG/view?usp=sharing"/>
-    <hyperlink ref="E27" r:id="rId24" location="slide=id.g368b57d9771_0_5" display="https://docs.google.com/presentation/d/1HQwwEbBNJQIcf6OTAs8pJy_D20Y0nqOVc06X70Mgfqo/edit?slide=id.g368b57d9771_0_5#slide=id.g368b57d9771_0_5"/>
-    <hyperlink ref="E28" r:id="rId25" location="slide=id.p" display="https://docs.google.com/presentation/d/1J5fJSWM7zRzUkobLcMHHhKTRADeeII_Wvi6oxsBuDfw/edit?slide=id.p#slide=id.p"/>
-    <hyperlink ref="E29" r:id="rId26" display="https://docs.google.com/presentation/d/1_HJsLPXQKMbV31pkUVZu21e63G57YJQwbfe-ei19kKs"/>
-    <hyperlink ref="E30" r:id="rId27" display="https://prezi.com/view/CAf5JqoNbJs3T4lpA1pX/?referral_token=S5on9plnB3FN"/>
-    <hyperlink ref="E33" r:id="rId28" display="https://docs.google.com/presentation/d/1i5-jm2SmBDBC0HV2_fLVSEPoUXw41zy98SM9nWcQ0eA/edit?usp=sharing"/>
-    <hyperlink ref="E34" r:id="rId29" display="https://docs.google.com/presentation/d/1SoVMWUZTTAbccWIN6PZzVrZ22a-bT59jkDu6jy_C_Ag/edit?usp=sharing"/>
-    <hyperlink ref="E35" r:id="rId30" display="https://docs.google.com/presentation/d/1oykfG53Luetf6qS9rQbfVchJPLp5Z5aspVP3-MJP8SI/edit?usp=sharing"/>
-    <hyperlink ref="E36" r:id="rId31" display="https://docs.google.com/presentation/d/1OIN85XF82k9_kRgkE9q-imG4W0Vh6CrW2nb0o1muUD0/edit"/>
-    <hyperlink ref="E37" r:id="rId32" display="https://docs.google.com/presentation/d/1FNRG9AFQwtfVy7D1UixxgZ4EYxmRnamw2_TD8189Mo0/edit?usp=sharing"/>
-    <hyperlink ref="B38" r:id="rId33" display="🎤 oscloud.cz"/>
-    <hyperlink ref="E38" r:id="rId34" display="https://docs.google.com/presentation/d/1hIApwqazJV29sxGV9bQLlB3Dih1ITAlFZtau88jM0CY/edit?usp=sharing"/>
-    <hyperlink ref="E39" r:id="rId35" display="https://docs.google.com/presentation/d/183ChRmG69cV7aB0YapOgMYxji5wGK0fM_lPcdvOMEBE/edit?usp=sharing"/>
-    <hyperlink ref="E40" r:id="rId36" display="https://docs.google.com/presentation/d/1s2GhXAiMA9MEqqI9qdawnF3HMOACa7s9wYvEQ9A3-Mk/edit?usp=sharing"/>
-    <hyperlink ref="E41" r:id="rId37" display="https://docs.google.com/presentation/d/1-pgcRAKRvaAMc9bQP3-BBffMF3YQQ5viYzAzoDalAWY/edit?usp=sharing"/>
-    <hyperlink ref="E42" r:id="rId38" display="https://docs.google.com/presentation/d/1BCavpivXPhLGHtPYNg60fjXb8o-m84FmXzsfMUQr0nI/edit"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://www.linkedin.com/in/vaclav-stolin/"/>
+    <hyperlink ref="E6" r:id="rId6" display="https://docs.google.com/presentation/d/1baofQPtOptpMkWzE3mQs7pgcmA3QcGPwpBu81ySnVuc/edit?usp=drivesdk"/>
+    <hyperlink ref="E7" r:id="rId7" location="slide=id.p" display="https://docs.google.com/presentation/d/1ZVa8tlptD4ETx3_L0R41AwlpGqD-ZeYbGGPoIsNKR-s/edit?slide=id.p#slide=id.p "/>
+    <hyperlink ref="C9" r:id="rId8" display="https://blog.zvestov.cz"/>
+    <hyperlink ref="E10" r:id="rId9" display="https://docs.google.com/presentation/d/1nQlBARhHV9sraosAbuwx4jwzlqiQuRVMPJQrrmI-UrY/edit?usp=sharing"/>
+    <hyperlink ref="C11" r:id="rId10" display="https://www.linkedin.com/in/petercipov/"/>
+    <hyperlink ref="E11" r:id="rId11" location="slide=id.p" display="https://docs.google.com/presentation/d/1DX90VUUTQTHT4s85VBWBN43GBFirI8lzUOLZtO3TJvE/edit?slide=id.p#slide=id.p"/>
+    <hyperlink ref="C12" r:id="rId12" display="https://omnifish.ee/"/>
+    <hyperlink ref="E12" r:id="rId13" display="https://docs.google.com/presentation/d/14LRfxMPL2mMEI-m1Xrv7GKwOtkhsB_-kQ41UEjqoyt4/edit?usp=sharing"/>
+    <hyperlink ref="C13" r:id="rId14" display="www.actiwerks.com"/>
+    <hyperlink ref="E13" r:id="rId15" display="https://www.actiwerks.com/presentations/HomomorphicEncryption.pdf"/>
+    <hyperlink ref="E14" r:id="rId16" location="slide=id.p" display="https://docs.google.com/presentation/d/1iskzWRg4N3dLp9iWLrXWqt7_GeYrRWu9w4msvO9Sd0A/edit?slide=id.p#slide=id.p "/>
+    <hyperlink ref="E15" r:id="rId17" location="slide=id.p" display="https://docs.google.com/presentation/d/1vrWq4I1eDehxUYT2vJzd90yOBvb0GH6lFhxnh7ZybgY/edit?slide=id.p#slide=id.p "/>
+    <hyperlink ref="E16" r:id="rId18" display="https://bit.ly/4nzz7Sg"/>
+    <hyperlink ref="C17" r:id="rId19" display="https://www.linkedin.com/in/pavel-kriz-cz/"/>
+    <hyperlink ref="E17" r:id="rId20" display="https://docs.google.com/presentation/d/1_gIeV3Yayd_yd0I7VBb5o6fDBwgqjD10fyieUisVUrg/edit?usp=sharing"/>
+    <hyperlink ref="C18" r:id="rId21" display="https://fnx.io"/>
+    <hyperlink ref="E18" r:id="rId22" location="slide=id.g38464b7e565_0_0" display="https://docs.google.com/presentation/d/1_k_a5E8ChJOP4pi_QMeZALAaT7QCg3k6Hqj6-Gswnlw/edit?slide=id.g38464b7e565_0_0#slide=id.g38464b7e565_0_0 "/>
+    <hyperlink ref="C19" r:id="rId23" display="dond.cz"/>
+    <hyperlink ref="E19" r:id="rId24" display="https://docs.google.com/presentation/d/1Lnc1VZmC_yCS0myQd7eYpR3um5HdpwRAUPBwSV7u4_Y/edit?usp=sharing"/>
+    <hyperlink ref="C20" r:id="rId25" display="https://www.linkedin.com/in/miloshavranek/"/>
+    <hyperlink ref="E20" r:id="rId26" display="https://docs.google.com/presentation/d/1G3819kDuzcq-0tqje3yindOIFtZd3alqyOA_k_wKDOw/edit?usp=sharing"/>
+    <hyperlink ref="C21" r:id="rId27" display="https://www.linkedin.com/in/daniel-crha/"/>
+    <hyperlink ref="E21" r:id="rId28" display="Hiring is Hard! - jOpenSpace 2025.pdf"/>
+    <hyperlink ref="E22" r:id="rId29" display="https://docs.google.com/presentation/d/1cX-y_wwQJBrKBl4Fk9SuXiXLDtkgMdtQwX0sea0oIe4/edit?usp=sharing"/>
+    <hyperlink ref="E23" r:id="rId30" display="https://minily.org/jopenspace2025-ivoshm"/>
+    <hyperlink ref="C24" r:id="rId31" display="https://www.linkedin.com/in/filip-sedlak/"/>
+    <hyperlink ref="E24" r:id="rId32" location="slide=id.g38906502ce2_0_63" display="https://docs.google.com/presentation/d/1Tz-NWpJbeVC8LHxkpTAc0NHV8kY0rx9Ny9vroMVVdHc/edit?slide=id.g38906502ce2_0_63#slide=id.g38906502ce2_0_63"/>
+    <hyperlink ref="C25" r:id="rId33" display="www.vojtechruzicka.com"/>
+    <hyperlink ref="E25" r:id="rId34" location="slide=id.p1" display="https://docs.google.com/presentation/d/1ufyRBMFrCzOMf2s-DWDc7kbopfJnfdOKIJ0BJGNHia4/edit?slide=id.p1#slide=id.p1 "/>
+    <hyperlink ref="C26" r:id="rId35" display="https://www.linkedin.com/in/dulak/"/>
+    <hyperlink ref="E26" r:id="rId36" display="https://drive.google.com/file/d/1hFg11Sd2R6f9aYeXqYdbHJGAUOKTtqrG/view?usp=sharing"/>
+    <hyperlink ref="E27" r:id="rId37" location="slide=id.g368b57d9771_0_5" display="https://docs.google.com/presentation/d/1HQwwEbBNJQIcf6OTAs8pJy_D20Y0nqOVc06X70Mgfqo/edit?slide=id.g368b57d9771_0_5#slide=id.g368b57d9771_0_5 "/>
+    <hyperlink ref="E28" r:id="rId38" location="slide=id.p" display="https://docs.google.com/presentation/d/1J5fJSWM7zRzUkobLcMHHhKTRADeeII_Wvi6oxsBuDfw/edit?slide=id.p#slide=id.p "/>
+    <hyperlink ref="E29" r:id="rId39" display="https://docs.google.com/presentation/d/1_HJsLPXQKMbV31pkUVZu21e63G57YJQwbfe-ei19kKs"/>
+    <hyperlink ref="E30" r:id="rId40" display="https://prezi.com/view/CAf5JqoNbJs3T4lpA1pX/?referral_token=S5on9plnB3FN"/>
+    <hyperlink ref="C32" r:id="rId41" display="https://www.nekola.cz"/>
+    <hyperlink ref="C33" r:id="rId42" display="notnullmakers.com"/>
+    <hyperlink ref="E33" r:id="rId43" display="https://docs.google.com/presentation/d/1i5-jm2SmBDBC0HV2_fLVSEPoUXw41zy98SM9nWcQ0eA/edit?usp=sharing"/>
+    <hyperlink ref="C34" r:id="rId44" display="https://commity.cz"/>
+    <hyperlink ref="E34" r:id="rId45" display="https://docs.google.com/presentation/d/1SoVMWUZTTAbccWIN6PZzVrZ22a-bT59jkDu6jy_C_Ag/edit?usp=sharing"/>
+    <hyperlink ref="C35" r:id="rId46" display="https://sika.io"/>
+    <hyperlink ref="E35" r:id="rId47" display="https://docs.google.com/presentation/d/1oykfG53Luetf6qS9rQbfVchJPLp5Z5aspVP3-MJP8SI/edit?usp=sharing"/>
+    <hyperlink ref="C36" r:id="rId48" display="https://filip-prochazka.com/"/>
+    <hyperlink ref="E36" r:id="rId49" display="https://docs.google.com/presentation/d/1OIN85XF82k9_kRgkE9q-imG4W0Vh6CrW2nb0o1muUD0/edit "/>
+    <hyperlink ref="C37" r:id="rId50" display="https://www.linkedin.com/in/xxbedy/"/>
+    <hyperlink ref="E37" r:id="rId51" display="https://docs.google.com/presentation/d/1FNRG9AFQwtfVy7D1UixxgZ4EYxmRnamw2_TD8189Mo0/edit?usp=sharing"/>
+    <hyperlink ref="B38" r:id="rId52" display="🎤 oscloud.cz"/>
+    <hyperlink ref="C38" r:id="rId53" display="https://calavera.info"/>
+    <hyperlink ref="E38" r:id="rId54" display="https://docs.google.com/presentation/d/1hIApwqazJV29sxGV9bQLlB3Dih1ITAlFZtau88jM0CY/edit?usp=sharing"/>
+    <hyperlink ref="C39" r:id="rId55" display="https://novoj.net"/>
+    <hyperlink ref="E39" r:id="rId56" display="https://docs.google.com/presentation/d/183ChRmG69cV7aB0YapOgMYxji5wGK0fM_lPcdvOMEBE/edit?usp=sharing"/>
+    <hyperlink ref="E40" r:id="rId57" display="https://docs.google.com/presentation/d/1s2GhXAiMA9MEqqI9qdawnF3HMOACa7s9wYvEQ9A3-Mk/edit?usp=sharing"/>
+    <hyperlink ref="E41" r:id="rId58" display="https://docs.google.com/presentation/d/1-pgcRAKRvaAMc9bQP3-BBffMF3YQQ5viYzAzoDalAWY/edit?usp=sharing"/>
+    <hyperlink ref="E42" r:id="rId59" display="https://docs.google.com/presentation/d/1BCavpivXPhLGHtPYNg60fjXb8o-m84FmXzsfMUQr0nI/edit "/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
